--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321259</v>
+        <v>132321257</v>
       </c>
       <c r="B2" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335124</v>
+        <v>334966</v>
       </c>
       <c r="R2" t="n">
         <v>6541514</v>
@@ -768,7 +768,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321257</v>
+        <v>132321259</v>
       </c>
       <c r="B3" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,7 +834,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334966</v>
+        <v>335124</v>
       </c>
       <c r="R3" t="n">
         <v>6541514</v>
@@ -879,12 +884,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1029,53 +1029,61 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321260</v>
+        <v>132321142</v>
       </c>
       <c r="B5" t="n">
-        <v>101301</v>
+        <v>58109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335149</v>
+        <v>335069</v>
       </c>
       <c r="R5" t="n">
-        <v>6541541</v>
+        <v>6541511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,19 +1118,28 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1140,61 +1157,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321142</v>
+        <v>132321260</v>
       </c>
       <c r="B6" t="n">
-        <v>58107</v>
+        <v>101304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335069</v>
+        <v>335149</v>
       </c>
       <c r="R6" t="n">
-        <v>6541511</v>
+        <v>6541541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,28 +1238,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
         <v>132321261</v>
       </c>
       <c r="B7" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132321169</v>
       </c>
       <c r="B8" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>132321125</v>
       </c>
       <c r="B9" t="n">
-        <v>96325</v>
+        <v>96328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>132321263</v>
       </c>
       <c r="B10" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321255</v>
+        <v>132321262</v>
       </c>
       <c r="B11" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335110</v>
+        <v>335199</v>
       </c>
       <c r="R11" t="n">
-        <v>6541573</v>
+        <v>6541563</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1812,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1830,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321262</v>
+        <v>132321255</v>
       </c>
       <c r="B12" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1867,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1873,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335199</v>
+        <v>335110</v>
       </c>
       <c r="R12" t="n">
-        <v>6541563</v>
+        <v>6541573</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,12 +1928,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Storvuxen äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
         <v>132321170</v>
       </c>
       <c r="B13" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>132321124</v>
       </c>
       <c r="B14" t="n">
-        <v>96325</v>
+        <v>96328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>132321172</v>
       </c>
       <c r="B15" t="n">
-        <v>97963</v>
+        <v>97966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>132321258</v>
       </c>
       <c r="B17" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>132321256</v>
       </c>
       <c r="B18" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -2417,7 +2417,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321258</v>
+        <v>132321256</v>
       </c>
       <c r="B17" t="n">
         <v>101304</v>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335103</v>
+        <v>335108</v>
       </c>
       <c r="R17" t="n">
-        <v>6541513</v>
+        <v>6541586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog.</t>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321256</v>
+        <v>132321258</v>
       </c>
       <c r="B18" t="n">
         <v>101304</v>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335108</v>
+        <v>335103</v>
       </c>
       <c r="R18" t="n">
-        <v>6541586</v>
+        <v>6541513</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321257</v>
+        <v>132321259</v>
       </c>
       <c r="B2" t="n">
         <v>101304</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334966</v>
+        <v>335124</v>
       </c>
       <c r="R2" t="n">
         <v>6541514</v>
@@ -768,12 +768,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321259</v>
+        <v>132321257</v>
       </c>
       <c r="B3" t="n">
         <v>101304</v>
@@ -834,7 +829,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335124</v>
+        <v>334966</v>
       </c>
       <c r="R3" t="n">
         <v>6541514</v>
@@ -884,7 +879,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1029,61 +1029,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321142</v>
+        <v>132321260</v>
       </c>
       <c r="B5" t="n">
-        <v>58109</v>
+        <v>101304</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335069</v>
+        <v>335149</v>
       </c>
       <c r="R5" t="n">
-        <v>6541511</v>
+        <v>6541541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,28 +1110,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,53 +1140,61 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321260</v>
+        <v>132321142</v>
       </c>
       <c r="B6" t="n">
-        <v>101304</v>
+        <v>58109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335149</v>
+        <v>335069</v>
       </c>
       <c r="R6" t="n">
-        <v>6541541</v>
+        <v>6541511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,19 +1229,28 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321262</v>
+        <v>132321170</v>
       </c>
       <c r="B11" t="n">
-        <v>101304</v>
+        <v>97963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,30 +1730,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1762,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335199</v>
+        <v>335382</v>
       </c>
       <c r="R11" t="n">
-        <v>6541563</v>
+        <v>6541761</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,6 +1796,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1813,11 +1814,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1946,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132321170</v>
+        <v>132321262</v>
       </c>
       <c r="B13" t="n">
-        <v>97963</v>
+        <v>101304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,26 +1953,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335382</v>
+        <v>335199</v>
       </c>
       <c r="R13" t="n">
-        <v>6541761</v>
+        <v>6541563</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,11 +2023,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer här i storväxt gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2041,6 +2036,11 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321256</v>
+        <v>132321258</v>
       </c>
       <c r="B17" t="n">
         <v>101304</v>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335108</v>
+        <v>335103</v>
       </c>
       <c r="R17" t="n">
-        <v>6541586</v>
+        <v>6541513</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321258</v>
+        <v>132321256</v>
       </c>
       <c r="B18" t="n">
         <v>101304</v>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335103</v>
+        <v>335108</v>
       </c>
       <c r="R18" t="n">
-        <v>6541513</v>
+        <v>6541586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog.</t>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321170</v>
+        <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>97963</v>
+        <v>101304</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,26 +1730,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1758,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335382</v>
+        <v>335110</v>
       </c>
       <c r="R11" t="n">
-        <v>6541761</v>
+        <v>6541573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,11 +1800,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer här i storväxt gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1813,7 +1812,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1831,7 +1830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321255</v>
+        <v>132321262</v>
       </c>
       <c r="B12" t="n">
         <v>101304</v>
@@ -1863,7 +1862,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1874,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335110</v>
+        <v>335199</v>
       </c>
       <c r="R12" t="n">
-        <v>6541573</v>
+        <v>6541563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1923,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1942,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132321262</v>
+        <v>132321170</v>
       </c>
       <c r="B13" t="n">
-        <v>101304</v>
+        <v>97963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,30 +1957,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335199</v>
+        <v>335382</v>
       </c>
       <c r="R13" t="n">
-        <v>6541563</v>
+        <v>6541761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,6 +2023,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2036,11 +2041,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321255</v>
+        <v>132321170</v>
       </c>
       <c r="B11" t="n">
-        <v>101304</v>
+        <v>97963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,30 +1730,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1762,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335110</v>
+        <v>335382</v>
       </c>
       <c r="R11" t="n">
-        <v>6541573</v>
+        <v>6541761</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,6 +1796,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1812,7 +1813,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1830,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321262</v>
+        <v>132321255</v>
       </c>
       <c r="B12" t="n">
         <v>101304</v>
@@ -1862,7 +1863,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1873,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335199</v>
+        <v>335110</v>
       </c>
       <c r="R12" t="n">
-        <v>6541563</v>
+        <v>6541573</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,12 +1924,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Storvuxen äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1946,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132321170</v>
+        <v>132321262</v>
       </c>
       <c r="B13" t="n">
-        <v>97963</v>
+        <v>101304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,26 +1953,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335382</v>
+        <v>335199</v>
       </c>
       <c r="R13" t="n">
-        <v>6541761</v>
+        <v>6541563</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,11 +2023,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer här i storväxt gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2041,6 +2036,11 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321259</v>
+        <v>132321257</v>
       </c>
       <c r="B2" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335124</v>
+        <v>334966</v>
       </c>
       <c r="R2" t="n">
         <v>6541514</v>
@@ -768,7 +768,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321257</v>
+        <v>132321259</v>
       </c>
       <c r="B3" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,7 +834,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334966</v>
+        <v>335124</v>
       </c>
       <c r="R3" t="n">
         <v>6541514</v>
@@ -879,12 +884,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -905,7 +905,7 @@
         <v>132321156</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,53 +1029,61 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321260</v>
+        <v>132321142</v>
       </c>
       <c r="B5" t="n">
-        <v>101304</v>
+        <v>58110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335149</v>
+        <v>335069</v>
       </c>
       <c r="R5" t="n">
-        <v>6541541</v>
+        <v>6541511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,19 +1118,28 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1140,61 +1157,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321142</v>
+        <v>132321260</v>
       </c>
       <c r="B6" t="n">
-        <v>58109</v>
+        <v>101312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335069</v>
+        <v>335149</v>
       </c>
       <c r="R6" t="n">
-        <v>6541511</v>
+        <v>6541541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,28 +1238,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
         <v>132321261</v>
       </c>
       <c r="B7" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132321169</v>
       </c>
       <c r="B8" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321125</v>
+        <v>132321263</v>
       </c>
       <c r="B9" t="n">
-        <v>96328</v>
+        <v>101312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,26 +1502,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1530,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335441</v>
+        <v>335368</v>
       </c>
       <c r="R9" t="n">
-        <v>6541708</v>
+        <v>6541759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1574,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321263</v>
+        <v>132321125</v>
       </c>
       <c r="B10" t="n">
-        <v>101304</v>
+        <v>96336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,30 +1618,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335368</v>
+        <v>335441</v>
       </c>
       <c r="R10" t="n">
-        <v>6541759</v>
+        <v>6541708</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
         <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321262</v>
+        <v>132321170</v>
       </c>
       <c r="B12" t="n">
-        <v>101304</v>
+        <v>97971</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,30 +1841,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1873,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335199</v>
+        <v>335382</v>
       </c>
       <c r="R12" t="n">
-        <v>6541563</v>
+        <v>6541761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,6 +1907,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1924,11 +1925,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1946,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132321170</v>
+        <v>132321262</v>
       </c>
       <c r="B13" t="n">
-        <v>97963</v>
+        <v>101312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,26 +1953,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335382</v>
+        <v>335199</v>
       </c>
       <c r="R13" t="n">
-        <v>6541761</v>
+        <v>6541563</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,11 +2023,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer här i storväxt gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2041,6 +2036,11 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
         <v>132321124</v>
       </c>
       <c r="B14" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>132321172</v>
       </c>
       <c r="B15" t="n">
-        <v>97966</v>
+        <v>97974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>132321154</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>132321258</v>
       </c>
       <c r="B17" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>132321256</v>
       </c>
       <c r="B18" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>132321157</v>
       </c>
       <c r="B19" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>132321134</v>
       </c>
       <c r="B20" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321263</v>
+        <v>132321125</v>
       </c>
       <c r="B9" t="n">
-        <v>101312</v>
+        <v>96336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,30 +1502,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335368</v>
+        <v>335441</v>
       </c>
       <c r="R9" t="n">
-        <v>6541759</v>
+        <v>6541708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1570,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321125</v>
+        <v>132321263</v>
       </c>
       <c r="B10" t="n">
-        <v>96336</v>
+        <v>101312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,26 +1614,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335441</v>
+        <v>335368</v>
       </c>
       <c r="R10" t="n">
-        <v>6541708</v>
+        <v>6541759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321257</v>
+        <v>132321259</v>
       </c>
       <c r="B2" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334966</v>
+        <v>335124</v>
       </c>
       <c r="R2" t="n">
         <v>6541514</v>
@@ -768,12 +768,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321259</v>
+        <v>132321257</v>
       </c>
       <c r="B3" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +829,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335124</v>
+        <v>334966</v>
       </c>
       <c r="R3" t="n">
         <v>6541514</v>
@@ -884,7 +879,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -905,7 +905,7 @@
         <v>132321156</v>
       </c>
       <c r="B4" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>132321142</v>
       </c>
       <c r="B5" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>132321260</v>
       </c>
       <c r="B6" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>132321261</v>
       </c>
       <c r="B7" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132321169</v>
       </c>
       <c r="B8" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321125</v>
+        <v>132321263</v>
       </c>
       <c r="B9" t="n">
-        <v>96336</v>
+        <v>101323</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,26 +1502,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1530,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335441</v>
+        <v>335368</v>
       </c>
       <c r="R9" t="n">
-        <v>6541708</v>
+        <v>6541759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1574,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321263</v>
+        <v>132321125</v>
       </c>
       <c r="B10" t="n">
-        <v>101312</v>
+        <v>96346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,30 +1618,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335368</v>
+        <v>335441</v>
       </c>
       <c r="R10" t="n">
-        <v>6541759</v>
+        <v>6541708</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
         <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>132321170</v>
       </c>
       <c r="B12" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>132321262</v>
       </c>
       <c r="B13" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>132321124</v>
       </c>
       <c r="B14" t="n">
-        <v>96336</v>
+        <v>96346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>132321172</v>
       </c>
       <c r="B15" t="n">
-        <v>97974</v>
+        <v>97984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>132321154</v>
       </c>
       <c r="B16" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>132321258</v>
       </c>
       <c r="B17" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>132321256</v>
       </c>
       <c r="B18" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>132321157</v>
       </c>
       <c r="B19" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>132321134</v>
       </c>
       <c r="B20" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132321259</v>
       </c>
       <c r="B2" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>132321257</v>
       </c>
       <c r="B3" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>132321260</v>
       </c>
       <c r="B6" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>132321261</v>
       </c>
       <c r="B7" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132321169</v>
       </c>
       <c r="B8" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321263</v>
+        <v>132321125</v>
       </c>
       <c r="B9" t="n">
-        <v>101323</v>
+        <v>96347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,30 +1502,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335368</v>
+        <v>335441</v>
       </c>
       <c r="R9" t="n">
-        <v>6541759</v>
+        <v>6541708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1570,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321125</v>
+        <v>132321263</v>
       </c>
       <c r="B10" t="n">
-        <v>96346</v>
+        <v>101324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,26 +1614,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335441</v>
+        <v>335368</v>
       </c>
       <c r="R10" t="n">
-        <v>6541708</v>
+        <v>6541759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
         <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321170</v>
+        <v>132321262</v>
       </c>
       <c r="B12" t="n">
-        <v>97981</v>
+        <v>101324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,26 +1841,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1869,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335382</v>
+        <v>335199</v>
       </c>
       <c r="R12" t="n">
-        <v>6541761</v>
+        <v>6541563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,11 +1911,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer här i storväxt gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1925,6 +1924,11 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1942,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132321262</v>
+        <v>132321170</v>
       </c>
       <c r="B13" t="n">
-        <v>101323</v>
+        <v>97982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,30 +1957,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335199</v>
+        <v>335382</v>
       </c>
       <c r="R13" t="n">
-        <v>6541563</v>
+        <v>6541761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,6 +2023,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2036,11 +2041,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
         <v>132321124</v>
       </c>
       <c r="B14" t="n">
-        <v>96346</v>
+        <v>96347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>132321172</v>
       </c>
       <c r="B15" t="n">
-        <v>97984</v>
+        <v>97985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,42 +2282,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132321154</v>
+        <v>132321258</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>101324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335053</v>
+        <v>335103</v>
       </c>
       <c r="R16" t="n">
-        <v>6541760</v>
+        <v>6541513</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,17 +2363,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2382,24 +2378,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2417,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321258</v>
+        <v>132321256</v>
       </c>
       <c r="B17" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335103</v>
+        <v>335108</v>
       </c>
       <c r="R17" t="n">
-        <v>6541513</v>
+        <v>6541586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2496,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog.</t>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2533,42 +2514,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321256</v>
+        <v>132321154</v>
       </c>
       <c r="B18" t="n">
-        <v>101323</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2576,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335108</v>
+        <v>335053</v>
       </c>
       <c r="R18" t="n">
-        <v>6541586</v>
+        <v>6541760</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,13 +2595,17 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2629,9 +2614,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132321259</v>
       </c>
       <c r="B2" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>132321257</v>
       </c>
       <c r="B3" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>132321260</v>
       </c>
       <c r="B6" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>132321261</v>
       </c>
       <c r="B7" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132321169</v>
       </c>
       <c r="B8" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321125</v>
+        <v>132321263</v>
       </c>
       <c r="B9" t="n">
-        <v>96347</v>
+        <v>101325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,26 +1502,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1530,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335441</v>
+        <v>335368</v>
       </c>
       <c r="R9" t="n">
-        <v>6541708</v>
+        <v>6541759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1574,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321263</v>
+        <v>132321125</v>
       </c>
       <c r="B10" t="n">
-        <v>101324</v>
+        <v>96348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,30 +1618,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335368</v>
+        <v>335441</v>
       </c>
       <c r="R10" t="n">
-        <v>6541759</v>
+        <v>6541708</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
         <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321262</v>
+        <v>132321170</v>
       </c>
       <c r="B12" t="n">
-        <v>101324</v>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,30 +1841,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1873,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335199</v>
+        <v>335382</v>
       </c>
       <c r="R12" t="n">
-        <v>6541563</v>
+        <v>6541761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,6 +1907,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1924,11 +1925,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1946,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132321170</v>
+        <v>132321262</v>
       </c>
       <c r="B13" t="n">
-        <v>97982</v>
+        <v>101325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,26 +1953,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335382</v>
+        <v>335199</v>
       </c>
       <c r="R13" t="n">
-        <v>6541761</v>
+        <v>6541563</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,11 +2023,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer här i storväxt gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2041,6 +2036,11 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
         <v>132321124</v>
       </c>
       <c r="B14" t="n">
-        <v>96347</v>
+        <v>96348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>132321172</v>
       </c>
       <c r="B15" t="n">
-        <v>97985</v>
+        <v>97986</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,42 +2282,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132321258</v>
+        <v>132321154</v>
       </c>
       <c r="B16" t="n">
-        <v>101324</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335103</v>
+        <v>335053</v>
       </c>
       <c r="R16" t="n">
-        <v>6541513</v>
+        <v>6541760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,13 +2363,17 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2378,9 +2382,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2398,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321256</v>
+        <v>132321258</v>
       </c>
       <c r="B17" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2441,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335108</v>
+        <v>335103</v>
       </c>
       <c r="R17" t="n">
-        <v>6541586</v>
+        <v>6541513</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2496,7 +2515,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2514,42 +2533,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321154</v>
+        <v>132321256</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>101325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2557,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335053</v>
+        <v>335108</v>
       </c>
       <c r="R18" t="n">
-        <v>6541760</v>
+        <v>6541586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,17 +2614,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2614,24 +2629,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321263</v>
+        <v>132321125</v>
       </c>
       <c r="B9" t="n">
-        <v>101325</v>
+        <v>96348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,30 +1502,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335368</v>
+        <v>335441</v>
       </c>
       <c r="R9" t="n">
-        <v>6541759</v>
+        <v>6541708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1570,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321125</v>
+        <v>132321263</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
+        <v>101325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,26 +1614,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335441</v>
+        <v>335368</v>
       </c>
       <c r="R10" t="n">
-        <v>6541708</v>
+        <v>6541759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2282,42 +2282,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132321154</v>
+        <v>132321258</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>101325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335053</v>
+        <v>335103</v>
       </c>
       <c r="R16" t="n">
-        <v>6541760</v>
+        <v>6541513</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,17 +2363,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2382,24 +2378,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2417,7 +2398,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321258</v>
+        <v>132321256</v>
       </c>
       <c r="B17" t="n">
         <v>101325</v>
@@ -2460,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335103</v>
+        <v>335108</v>
       </c>
       <c r="R17" t="n">
-        <v>6541513</v>
+        <v>6541586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2496,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog.</t>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2533,42 +2514,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321256</v>
+        <v>132321154</v>
       </c>
       <c r="B18" t="n">
-        <v>101325</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2576,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335108</v>
+        <v>335053</v>
       </c>
       <c r="R18" t="n">
-        <v>6541586</v>
+        <v>6541760</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,13 +2595,17 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2629,9 +2614,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132321259</v>
       </c>
       <c r="B2" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>132321257</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>132321260</v>
       </c>
       <c r="B6" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>132321261</v>
       </c>
       <c r="B7" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>132321263</v>
       </c>
       <c r="B10" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>132321262</v>
       </c>
       <c r="B13" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2282,42 +2282,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132321258</v>
+        <v>132321154</v>
       </c>
       <c r="B16" t="n">
-        <v>101325</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335103</v>
+        <v>335053</v>
       </c>
       <c r="R16" t="n">
-        <v>6541513</v>
+        <v>6541760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,13 +2363,17 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2378,9 +2382,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2398,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321256</v>
+        <v>132321258</v>
       </c>
       <c r="B17" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2441,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335108</v>
+        <v>335103</v>
       </c>
       <c r="R17" t="n">
-        <v>6541586</v>
+        <v>6541513</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2496,7 +2515,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2514,42 +2533,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321154</v>
+        <v>132321256</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2557,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335053</v>
+        <v>335108</v>
       </c>
       <c r="R18" t="n">
-        <v>6541760</v>
+        <v>6541586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,17 +2614,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2614,24 +2629,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -1029,61 +1029,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321142</v>
+        <v>132321260</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335069</v>
+        <v>335149</v>
       </c>
       <c r="R5" t="n">
-        <v>6541511</v>
+        <v>6541541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,28 +1110,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,53 +1140,61 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321260</v>
+        <v>132321142</v>
       </c>
       <c r="B6" t="n">
-        <v>101326</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335149</v>
+        <v>335069</v>
       </c>
       <c r="R6" t="n">
-        <v>6541541</v>
+        <v>6541511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,19 +1229,28 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132321259</v>
       </c>
       <c r="B2" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>132321257</v>
       </c>
       <c r="B3" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>132321156</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>132321260</v>
       </c>
       <c r="B5" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>132321142</v>
       </c>
       <c r="B6" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>132321261</v>
       </c>
       <c r="B7" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132321169</v>
       </c>
       <c r="B8" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>132321125</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>132321263</v>
       </c>
       <c r="B10" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>132321170</v>
       </c>
       <c r="B12" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>132321262</v>
       </c>
       <c r="B13" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>132321124</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>132321172</v>
       </c>
       <c r="B15" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,42 +2282,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132321154</v>
+        <v>132321258</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>101327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335053</v>
+        <v>335103</v>
       </c>
       <c r="R16" t="n">
-        <v>6541760</v>
+        <v>6541513</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,17 +2363,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2382,24 +2378,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2417,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321258</v>
+        <v>132321256</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335103</v>
+        <v>335108</v>
       </c>
       <c r="R17" t="n">
-        <v>6541513</v>
+        <v>6541586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2496,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog.</t>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2533,42 +2514,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321256</v>
+        <v>132321154</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>57951</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2576,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335108</v>
+        <v>335053</v>
       </c>
       <c r="R18" t="n">
-        <v>6541586</v>
+        <v>6541760</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,13 +2595,17 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2629,9 +2614,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2652,7 +2652,7 @@
         <v>132321157</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>132321134</v>
       </c>
       <c r="B20" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132321259</v>
       </c>
       <c r="B2" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>132321257</v>
       </c>
       <c r="B3" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,53 +1029,61 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321260</v>
+        <v>132321142</v>
       </c>
       <c r="B5" t="n">
-        <v>101327</v>
+        <v>58115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335149</v>
+        <v>335069</v>
       </c>
       <c r="R5" t="n">
-        <v>6541541</v>
+        <v>6541511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,19 +1118,28 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1140,61 +1157,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321142</v>
+        <v>132321260</v>
       </c>
       <c r="B6" t="n">
-        <v>58115</v>
+        <v>101329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335069</v>
+        <v>335149</v>
       </c>
       <c r="R6" t="n">
-        <v>6541511</v>
+        <v>6541541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,28 +1238,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
         <v>132321261</v>
       </c>
       <c r="B7" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132321169</v>
       </c>
       <c r="B8" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321125</v>
+        <v>132321263</v>
       </c>
       <c r="B9" t="n">
-        <v>96349</v>
+        <v>101329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,26 +1502,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1530,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335441</v>
+        <v>335368</v>
       </c>
       <c r="R9" t="n">
-        <v>6541708</v>
+        <v>6541759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1574,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321263</v>
+        <v>132321125</v>
       </c>
       <c r="B10" t="n">
-        <v>101327</v>
+        <v>96351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,30 +1618,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335368</v>
+        <v>335441</v>
       </c>
       <c r="R10" t="n">
-        <v>6541759</v>
+        <v>6541708</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
         <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321170</v>
+        <v>132321262</v>
       </c>
       <c r="B12" t="n">
-        <v>97984</v>
+        <v>101329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,26 +1841,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1869,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335382</v>
+        <v>335199</v>
       </c>
       <c r="R12" t="n">
-        <v>6541761</v>
+        <v>6541563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,11 +1911,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer här i storväxt gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1925,6 +1924,11 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1942,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132321262</v>
+        <v>132321170</v>
       </c>
       <c r="B13" t="n">
-        <v>101327</v>
+        <v>97986</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,30 +1957,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335199</v>
+        <v>335382</v>
       </c>
       <c r="R13" t="n">
-        <v>6541563</v>
+        <v>6541761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,6 +2023,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2036,11 +2041,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
         <v>132321124</v>
       </c>
       <c r="B14" t="n">
-        <v>96349</v>
+        <v>96351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>132321172</v>
       </c>
       <c r="B15" t="n">
-        <v>97987</v>
+        <v>97989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,42 +2282,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132321258</v>
+        <v>132321154</v>
       </c>
       <c r="B16" t="n">
-        <v>101327</v>
+        <v>57951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335103</v>
+        <v>335053</v>
       </c>
       <c r="R16" t="n">
-        <v>6541513</v>
+        <v>6541760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,13 +2363,17 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2378,9 +2382,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2398,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321256</v>
+        <v>132321258</v>
       </c>
       <c r="B17" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2441,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335108</v>
+        <v>335103</v>
       </c>
       <c r="R17" t="n">
-        <v>6541586</v>
+        <v>6541513</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2496,7 +2515,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2514,42 +2533,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321154</v>
+        <v>132321256</v>
       </c>
       <c r="B18" t="n">
-        <v>57951</v>
+        <v>101329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2557,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335053</v>
+        <v>335108</v>
       </c>
       <c r="R18" t="n">
-        <v>6541760</v>
+        <v>6541586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,17 +2614,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2614,24 +2629,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132321259</v>
       </c>
       <c r="B2" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>132321257</v>
       </c>
       <c r="B3" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,61 +1029,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321142</v>
+        <v>132321260</v>
       </c>
       <c r="B5" t="n">
-        <v>58115</v>
+        <v>101330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335069</v>
+        <v>335149</v>
       </c>
       <c r="R5" t="n">
-        <v>6541511</v>
+        <v>6541541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,28 +1110,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,53 +1140,61 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321260</v>
+        <v>132321142</v>
       </c>
       <c r="B6" t="n">
-        <v>101329</v>
+        <v>58115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335149</v>
+        <v>335069</v>
       </c>
       <c r="R6" t="n">
-        <v>6541541</v>
+        <v>6541511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,19 +1229,28 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
         <v>132321261</v>
       </c>
       <c r="B7" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132321169</v>
       </c>
       <c r="B8" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>132321263</v>
       </c>
       <c r="B9" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>132321125</v>
       </c>
       <c r="B10" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>132321262</v>
       </c>
       <c r="B12" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>132321170</v>
       </c>
       <c r="B13" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>132321124</v>
       </c>
       <c r="B14" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>132321172</v>
       </c>
       <c r="B15" t="n">
-        <v>97989</v>
+        <v>97990</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,42 +2282,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132321154</v>
+        <v>132321258</v>
       </c>
       <c r="B16" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335053</v>
+        <v>335103</v>
       </c>
       <c r="R16" t="n">
-        <v>6541760</v>
+        <v>6541513</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,17 +2363,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2382,24 +2378,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2417,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321258</v>
+        <v>132321256</v>
       </c>
       <c r="B17" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335103</v>
+        <v>335108</v>
       </c>
       <c r="R17" t="n">
-        <v>6541513</v>
+        <v>6541586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2496,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog.</t>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2533,42 +2514,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321256</v>
+        <v>132321154</v>
       </c>
       <c r="B18" t="n">
-        <v>101329</v>
+        <v>57951</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2576,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335108</v>
+        <v>335053</v>
       </c>
       <c r="R18" t="n">
-        <v>6541586</v>
+        <v>6541760</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,13 +2595,17 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2629,9 +2614,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -1029,53 +1029,61 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321260</v>
+        <v>132321142</v>
       </c>
       <c r="B5" t="n">
-        <v>101330</v>
+        <v>58115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335149</v>
+        <v>335069</v>
       </c>
       <c r="R5" t="n">
-        <v>6541541</v>
+        <v>6541511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,19 +1118,28 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1140,61 +1157,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321142</v>
+        <v>132321260</v>
       </c>
       <c r="B6" t="n">
-        <v>58115</v>
+        <v>101330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335069</v>
+        <v>335149</v>
       </c>
       <c r="R6" t="n">
-        <v>6541511</v>
+        <v>6541541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,28 +1238,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321255</v>
+        <v>132321170</v>
       </c>
       <c r="B11" t="n">
-        <v>101330</v>
+        <v>97987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,30 +1730,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1762,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335110</v>
+        <v>335382</v>
       </c>
       <c r="R11" t="n">
-        <v>6541573</v>
+        <v>6541761</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,6 +1796,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1812,7 +1813,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1830,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321262</v>
+        <v>132321255</v>
       </c>
       <c r="B12" t="n">
         <v>101330</v>
@@ -1862,7 +1863,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1873,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335199</v>
+        <v>335110</v>
       </c>
       <c r="R12" t="n">
-        <v>6541563</v>
+        <v>6541573</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,12 +1924,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Storvuxen äldre granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1946,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132321170</v>
+        <v>132321262</v>
       </c>
       <c r="B13" t="n">
-        <v>97987</v>
+        <v>101330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,26 +1953,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335382</v>
+        <v>335199</v>
       </c>
       <c r="R13" t="n">
-        <v>6541761</v>
+        <v>6541563</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,11 +2023,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer här i storväxt gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2041,6 +2036,11 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321170</v>
+        <v>132321255</v>
       </c>
       <c r="B11" t="n">
-        <v>97987</v>
+        <v>101330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,26 +1730,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1758,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335382</v>
+        <v>335110</v>
       </c>
       <c r="R11" t="n">
-        <v>6541761</v>
+        <v>6541573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,11 +1800,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer här i storväxt gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1813,7 +1812,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1831,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321255</v>
+        <v>132321170</v>
       </c>
       <c r="B12" t="n">
-        <v>101330</v>
+        <v>97987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,30 +1841,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1874,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335110</v>
+        <v>335382</v>
       </c>
       <c r="R12" t="n">
-        <v>6541573</v>
+        <v>6541761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,6 +1907,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2282,42 +2282,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132321258</v>
+        <v>132321154</v>
       </c>
       <c r="B16" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335103</v>
+        <v>335053</v>
       </c>
       <c r="R16" t="n">
-        <v>6541513</v>
+        <v>6541760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,13 +2363,17 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2378,9 +2382,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2398,7 +2417,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321256</v>
+        <v>132321258</v>
       </c>
       <c r="B17" t="n">
         <v>101330</v>
@@ -2441,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335108</v>
+        <v>335103</v>
       </c>
       <c r="R17" t="n">
-        <v>6541586</v>
+        <v>6541513</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2496,7 +2515,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2514,42 +2533,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321154</v>
+        <v>132321256</v>
       </c>
       <c r="B18" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2557,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335053</v>
+        <v>335108</v>
       </c>
       <c r="R18" t="n">
-        <v>6541760</v>
+        <v>6541586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,17 +2614,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2614,24 +2629,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrblandskog med inslag av asp och björk.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321263</v>
+        <v>132321125</v>
       </c>
       <c r="B9" t="n">
-        <v>101330</v>
+        <v>96352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,30 +1502,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335368</v>
+        <v>335441</v>
       </c>
       <c r="R9" t="n">
-        <v>6541759</v>
+        <v>6541708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1570,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321125</v>
+        <v>132321263</v>
       </c>
       <c r="B10" t="n">
-        <v>96352</v>
+        <v>101330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,26 +1614,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335441</v>
+        <v>335368</v>
       </c>
       <c r="R10" t="n">
-        <v>6541708</v>
+        <v>6541759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>133587830</v>
       </c>
       <c r="B19" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321259</v>
+        <v>133587830</v>
       </c>
       <c r="B2" t="n">
-        <v>101333</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelskog söder om Södra Backen, Dls</t>
+          <t>Södra Backen, bäckdal ca 600 m söder om, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335124</v>
+        <v>335068</v>
       </c>
       <c r="R2" t="n">
-        <v>6541514</v>
+        <v>6541718</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,34 +754,38 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, sluttning mot bäck.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321257</v>
+        <v>132321124</v>
       </c>
       <c r="B3" t="n">
-        <v>101333</v>
+        <v>96423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,30 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -829,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334966</v>
+        <v>335207</v>
       </c>
       <c r="R3" t="n">
-        <v>6541514</v>
+        <v>6541594</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,6 +859,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I äldre barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -880,11 +877,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,65 +894,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132321156</v>
+        <v>132321125</v>
       </c>
       <c r="B4" t="n">
-        <v>57954</v>
+        <v>96423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335115</v>
+        <v>335441</v>
       </c>
       <c r="R4" t="n">
-        <v>6541539</v>
+        <v>6541708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Synobservation av en trummade hane på en tallhögstubbe intill en nyuppbruten väg. I området kring fyndplatsen finns gott om lämpliga boträd av asp och tall och gott om stående död ved av främst gran där många stående döda granar är av grövre dimensioner.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,12 +982,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1029,61 +1006,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321142</v>
+        <v>132321213</v>
       </c>
       <c r="B5" t="n">
-        <v>58118</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335069</v>
+        <v>335079</v>
       </c>
       <c r="R5" t="n">
-        <v>6541511</v>
+        <v>6541664</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,28 +1083,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321260</v>
+        <v>132321214</v>
       </c>
       <c r="B6" t="n">
-        <v>101333</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,30 +1124,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335149</v>
+        <v>335147</v>
       </c>
       <c r="R6" t="n">
-        <v>6541541</v>
+        <v>6541538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132321261</v>
+        <v>132321215</v>
       </c>
       <c r="B7" t="n">
-        <v>101333</v>
+        <v>96410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,30 +1231,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335177</v>
+        <v>335175</v>
       </c>
       <c r="R7" t="n">
-        <v>6541560</v>
+        <v>6541559</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,6 +1297,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i granskog.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1361,7 +1314,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1379,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132321169</v>
+        <v>132321216</v>
       </c>
       <c r="B8" t="n">
-        <v>97990</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1418,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335098</v>
+        <v>335208</v>
       </c>
       <c r="R8" t="n">
-        <v>6541663</v>
+        <v>6541594</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I storvuxen gammal granskog.</t>
+          <t>I äldre grandominerad barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,7 +1426,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1491,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321125</v>
+        <v>132321154</v>
       </c>
       <c r="B9" t="n">
-        <v>96355</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,27 +1455,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1530,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335441</v>
+        <v>335053</v>
       </c>
       <c r="R9" t="n">
-        <v>6541708</v>
+        <v>6541760</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1527,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,13 +1536,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1603,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321263</v>
+        <v>132321156</v>
       </c>
       <c r="B10" t="n">
-        <v>101333</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,42 +1590,54 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335368</v>
+        <v>335115</v>
       </c>
       <c r="R10" t="n">
-        <v>6541759</v>
+        <v>6541539</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1674,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+          <t>Synobservation av en trummade hane på en tallhögstubbe intill en nyuppbruten väg. I området kring fyndplatsen finns gott om lämpliga boträd av asp och tall och gott om stående död ved av främst gran där många stående döda granar är av grövre dimensioner.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,13 +1683,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1719,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321255</v>
+        <v>132321157</v>
       </c>
       <c r="B11" t="n">
-        <v>101333</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,31 +1717,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1762,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335110</v>
+        <v>335547</v>
       </c>
       <c r="R11" t="n">
-        <v>6541573</v>
+        <v>6541768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,19 +1787,43 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1830,10 +1841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321170</v>
+        <v>132321134</v>
       </c>
       <c r="B12" t="n">
-        <v>97990</v>
+        <v>57162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,27 +1852,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1869,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335382</v>
+        <v>335481</v>
       </c>
       <c r="R12" t="n">
-        <v>6541761</v>
+        <v>6541651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1924,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Växer här i storväxt gammal granskog.</t>
+          <t>Färsk spillning i hög i gles öppen tallskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,13 +1933,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1942,53 +1956,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132321262</v>
+        <v>132321142</v>
       </c>
       <c r="B13" t="n">
-        <v>101333</v>
+        <v>58136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>335199</v>
+        <v>335069</v>
       </c>
       <c r="R13" t="n">
-        <v>6541563</v>
+        <v>6541511</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,24 +2045,28 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Storvuxen äldre granskog.</t>
+          <t>Bitvis flerskiktad äldre barrblandskog. På senare tid har här underröjts vilket missgynnar talltita.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2058,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132321124</v>
+        <v>132321133</v>
       </c>
       <c r="B14" t="n">
-        <v>96355</v>
+        <v>58131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,38 +2095,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>103023</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>335207</v>
+        <v>335098</v>
       </c>
       <c r="R14" t="n">
-        <v>6541594</v>
+        <v>6541886</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,18 +2173,12 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I äldre barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2170,10 +2202,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132321172</v>
+        <v>132321188</v>
       </c>
       <c r="B15" t="n">
-        <v>97993</v>
+        <v>111153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,16 +2213,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>220240</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2200,7 +2232,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2209,10 +2245,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>335061</v>
+        <v>335034</v>
       </c>
       <c r="R15" t="n">
-        <v>6541618</v>
+        <v>6541821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,11 +2283,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer här på marken i luckig barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2265,6 +2296,11 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2282,42 +2318,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132321154</v>
+        <v>132321189</v>
       </c>
       <c r="B16" t="n">
-        <v>57954</v>
+        <v>111153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220240</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335053</v>
+        <v>335157</v>
       </c>
       <c r="R16" t="n">
-        <v>6541760</v>
+        <v>6541636</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,7 +2401,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i stambasen av en stående död tall.</t>
+          <t>I gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,32 +2410,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2417,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132321258</v>
+        <v>132321190</v>
       </c>
       <c r="B17" t="n">
-        <v>101333</v>
+        <v>111153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,28 +2445,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220240</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2460,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>335103</v>
+        <v>335108</v>
       </c>
       <c r="R17" t="n">
-        <v>6541513</v>
+        <v>6541589</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,6 +2515,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I granskog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2510,12 +2532,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2533,10 +2550,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132321256</v>
+        <v>132321191</v>
       </c>
       <c r="B18" t="n">
-        <v>101333</v>
+        <v>111153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2544,28 +2561,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220240</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2576,10 +2593,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>335108</v>
+        <v>335002</v>
       </c>
       <c r="R18" t="n">
-        <v>6541586</v>
+        <v>6541508</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,12 +2643,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog med inslag av asp och björk.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2649,45 +2661,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133587830</v>
+        <v>132321192</v>
       </c>
       <c r="B19" t="n">
-        <v>97428</v>
+        <v>111153</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220240</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Backen, bäckdal ca 600 m söder om, Dls</t>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>335068</v>
+        <v>334941</v>
       </c>
       <c r="R19" t="n">
-        <v>6541718</v>
+        <v>6541565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,12 +2734,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,70 +2748,66 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Äldre barrskog, sluttning mot bäck.</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>På murken granlåga.</t>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132321157</v>
+        <v>132321193</v>
       </c>
       <c r="B20" t="n">
-        <v>57954</v>
+        <v>111153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220240</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2799,10 +2815,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>335547</v>
+        <v>334966</v>
       </c>
       <c r="R20" t="n">
-        <v>6541768</v>
+        <v>6541530</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2837,43 +2853,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2891,10 +2883,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132321134</v>
+        <v>132321194</v>
       </c>
       <c r="B21" t="n">
-        <v>57145</v>
+        <v>111153</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,31 +2894,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220240</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2934,10 +2926,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>335481</v>
+        <v>335101</v>
       </c>
       <c r="R21" t="n">
-        <v>6541651</v>
+        <v>6541512</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,23 +2964,19 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färsk spillning i hög i gles öppen tallskog.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3003,6 +2991,3030 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132321195</v>
+      </c>
+      <c r="B22" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>335202</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6541563</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132321196</v>
+      </c>
+      <c r="B23" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>335248</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6541674</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132321197</v>
+      </c>
+      <c r="B24" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>335379</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6541508</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I gammal barrblandskog med gott om grova granar i en ravinliknande markformation.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132321198</v>
+      </c>
+      <c r="B25" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>335533</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6541747</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I äldre barrblandskog med gott om stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132321199</v>
+      </c>
+      <c r="B26" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>335578</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6541749</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Barrblandskog med inslag av björk och asp.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132321200</v>
+      </c>
+      <c r="B27" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>335071</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6541912</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132321264</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>335040</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6541756</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132321265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>335415</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6541719</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132321268</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>335075</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6541892</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132321169</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>335098</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6541663</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>I storvuxen gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132321170</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>335382</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6541761</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132321172</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>335061</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6541618</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Växer här på marken i luckig barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132321255</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>335110</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6541573</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132321256</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>335108</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6541586</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Barrblandskog med inslag av asp och björk.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132321257</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>334966</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6541514</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132321258</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>335103</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6541513</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132321259</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>335124</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6541514</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132321260</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>335149</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6541541</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132321261</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>335177</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6541560</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132321262</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>335199</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6541563</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Storvuxen äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132321263</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>335368</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6541759</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132321237</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>335089</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6541788</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Växer på marken i en luckig yta i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132321238</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>335061</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6541618</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132321239</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>335450</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6541907</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Gles tallskog med inslag av björk och gran.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132321243</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>334926</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6541550</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fyndplats i luckig öppen äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132321244</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>335290</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6541569</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>I äldre gles talldominerad barrblandskog som är avverkningsanmäld. Basväg planerad och snitslad här.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132321245</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>335475</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6541656</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Gles talldominerad skog.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9465-2026 artfynd.xlsx
+++ b/artfynd/A 9465-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133587830</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321124</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321125</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321213</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321214</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321215</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321216</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321154</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1703,6 +1748,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321156</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1838,6 +1888,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321157</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321134</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2081,6 +2141,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321142</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2199,6 +2264,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321133</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2315,6 +2385,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321188</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2431,6 +2506,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321189</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2547,6 +2627,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321190</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2658,6 +2743,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321191</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2769,6 +2859,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321192</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2880,6 +2975,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321193</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2991,6 +3091,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321194</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3102,6 +3207,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321195</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3218,6 +3328,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321196</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3334,6 +3449,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321197</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3450,6 +3570,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321198</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3566,6 +3691,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321199</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3673,6 +3803,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321200</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3780,6 +3915,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321264</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3887,6 +4027,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321265</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3994,6 +4139,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321268</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4106,6 +4256,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321169</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4218,6 +4373,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321170</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4330,6 +4490,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321172</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4441,6 +4606,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321255</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4557,6 +4727,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321256</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4673,6 +4848,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321257</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4789,6 +4969,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321258</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4900,6 +5085,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321259</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5011,6 +5201,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321260</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5122,6 +5317,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321261</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5238,6 +5438,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321262</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5354,6 +5559,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321263</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5465,6 +5675,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321237</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5571,6 +5786,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321238</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5682,6 +5902,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321239</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5793,6 +6018,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321243</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5904,6 +6134,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321244</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6015,8 +6250,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321245</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>